--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ПАНТЕКС АГРО ЕООД/ПАНТЕКС АГРО ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ПАНТЕКС АГРО ЕООД/ПАНТЕКС АГРО ЕООД.xlsx
@@ -7,14 +7,14 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Data" sheetId="1" r:id="rId1"/>
+    <sheet name="ПАНТЕКС АГРО ЕООД" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="61">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -70,6 +73,36 @@
     <t>2026-05-13</t>
   </si>
   <si>
+    <t>2026-05-17</t>
+  </si>
+  <si>
+    <t>2026-05-22</t>
+  </si>
+  <si>
+    <t>2026-05-27</t>
+  </si>
+  <si>
+    <t>2026-05-29</t>
+  </si>
+  <si>
+    <t>2026-05-30</t>
+  </si>
+  <si>
+    <t>1911 O5 Варна</t>
+  </si>
+  <si>
+    <t>1147 Варна Ситроен</t>
+  </si>
+  <si>
+    <t>1918 O5 Търговище</t>
+  </si>
+  <si>
+    <t>1195 243 Тракия Езеро</t>
+  </si>
+  <si>
+    <t>1167 В. Търново вход</t>
+  </si>
+  <si>
     <t>78970154027720249</t>
   </si>
   <si>
@@ -79,22 +112,73 @@
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
-    <t>06:18</t>
-  </si>
-  <si>
-    <t>10:10</t>
-  </si>
-  <si>
-    <t>19:16</t>
-  </si>
-  <si>
-    <t>13:48</t>
-  </si>
-  <si>
-    <t>09:23</t>
-  </si>
-  <si>
-    <t>17:29</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>06:18:00</t>
+  </si>
+  <si>
+    <t>10:11:00</t>
+  </si>
+  <si>
+    <t>19:16:00</t>
+  </si>
+  <si>
+    <t>13:48:00</t>
+  </si>
+  <si>
+    <t>09:21:00</t>
+  </si>
+  <si>
+    <t>17:29:00</t>
+  </si>
+  <si>
+    <t>13:52:00</t>
+  </si>
+  <si>
+    <t>07:33:00</t>
+  </si>
+  <si>
+    <t>07:54:00</t>
+  </si>
+  <si>
+    <t>06:56:00</t>
+  </si>
+  <si>
+    <t>11:29:00</t>
+  </si>
+  <si>
+    <t>3231436459 3231436459</t>
+  </si>
+  <si>
+    <t>3231595643 3231595643</t>
+  </si>
+  <si>
+    <t>3231605740 3231605740</t>
+  </si>
+  <si>
+    <t>3231654913 3231654913</t>
+  </si>
+  <si>
+    <t>3231681858 3231681858</t>
+  </si>
+  <si>
+    <t>3231828507 3231828507</t>
+  </si>
+  <si>
+    <t>3232023109 3232023109</t>
+  </si>
+  <si>
+    <t>3232243692 3232243692</t>
+  </si>
+  <si>
+    <t>3232457057 3232457057</t>
+  </si>
+  <si>
+    <t>3232497291 3232497291</t>
+  </si>
+  <si>
+    <t>3232621616 3232621616</t>
   </si>
   <si>
     <t>Общи литри по продукт / ПАНТЕКС АГРО ЕООД</t>
@@ -518,24 +602,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:N18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
     <col min="2" max="2" width="18.7109375" customWidth="1"/>
     <col min="3" max="3" width="20.7109375" customWidth="1"/>
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
-    <col min="5" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="22.7109375" customWidth="1"/>
+    <col min="6" max="6" width="18.7109375" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -575,324 +661,565 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2">
-        <v>1911</v>
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>24</v>
       </c>
       <c r="C2">
         <v>11</v>
       </c>
       <c r="D2" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="E2" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="F2">
         <v>66.45</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H2">
         <v>1.44</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>95.69</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.52</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>101</v>
       </c>
-      <c r="K2" t="s">
-        <v>21</v>
-      </c>
-      <c r="L2">
+      <c r="L2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M2">
         <v>0</v>
       </c>
-      <c r="M2">
-        <v>174277</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
+      <c r="N2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3">
-        <v>1147</v>
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>25</v>
       </c>
       <c r="C3">
         <v>11</v>
       </c>
       <c r="D3" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="E3" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="F3">
         <v>50</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H3">
         <v>1.47</v>
       </c>
-      <c r="H3">
+      <c r="I3" s="1">
         <v>73.5</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3">
         <v>1.53</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="1">
         <v>76.5</v>
       </c>
-      <c r="K3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L3">
+      <c r="L3" t="s">
+        <v>34</v>
+      </c>
+      <c r="M3">
         <v>0</v>
       </c>
-      <c r="M3">
-        <v>178066</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+      <c r="N3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4">
-        <v>1918</v>
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>26</v>
       </c>
       <c r="C4">
         <v>10</v>
       </c>
       <c r="D4" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="E4" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="F4">
         <v>35</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H4">
         <v>1.47</v>
       </c>
-      <c r="H4">
+      <c r="I4" s="1">
         <v>51.45</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4">
         <v>1.53</v>
       </c>
-      <c r="J4">
+      <c r="K4" s="1">
         <v>53.55</v>
       </c>
-      <c r="K4" t="s">
-        <v>23</v>
-      </c>
-      <c r="L4">
+      <c r="L4" t="s">
+        <v>35</v>
+      </c>
+      <c r="M4">
         <v>0</v>
       </c>
-      <c r="M4">
-        <v>195597</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
+      <c r="N4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5">
-        <v>1911</v>
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>24</v>
       </c>
       <c r="C5">
         <v>11</v>
       </c>
       <c r="D5" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="E5" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="F5">
         <v>33.43</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H5">
         <v>1.47</v>
       </c>
-      <c r="H5">
+      <c r="I5" s="1">
         <v>49.14</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J5">
         <v>1.54</v>
       </c>
-      <c r="J5">
+      <c r="K5" s="1">
         <v>51.48</v>
       </c>
-      <c r="K5" t="s">
-        <v>24</v>
-      </c>
-      <c r="L5">
+      <c r="L5" t="s">
+        <v>36</v>
+      </c>
+      <c r="M5">
         <v>0</v>
       </c>
-      <c r="M5">
-        <v>104791</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
+      <c r="N5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6">
-        <v>1195</v>
+        <v>17</v>
+      </c>
+      <c r="B6" t="s">
+        <v>27</v>
       </c>
       <c r="C6">
         <v>11</v>
       </c>
       <c r="D6" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="E6" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="F6">
         <v>67.31999999999999</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H6">
         <v>1.47</v>
       </c>
-      <c r="H6">
+      <c r="I6" s="1">
         <v>98.95999999999999</v>
       </c>
-      <c r="I6" s="1">
+      <c r="J6">
         <v>1.55</v>
       </c>
-      <c r="J6">
+      <c r="K6" s="1">
         <v>104.35</v>
       </c>
-      <c r="K6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L6">
+      <c r="L6" t="s">
+        <v>37</v>
+      </c>
+      <c r="M6">
         <v>0</v>
       </c>
-      <c r="M6">
-        <v>228311</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
+      <c r="N6" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7">
-        <v>1911</v>
+        <v>18</v>
+      </c>
+      <c r="B7" t="s">
+        <v>24</v>
       </c>
       <c r="C7">
         <v>11</v>
       </c>
       <c r="D7" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="E7" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="F7">
         <v>71.77</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G7" t="s">
+        <v>32</v>
+      </c>
+      <c r="H7">
         <v>1.48</v>
       </c>
-      <c r="H7">
+      <c r="I7" s="1">
         <v>106.22</v>
       </c>
-      <c r="I7" s="1">
+      <c r="J7">
         <v>1.54</v>
       </c>
-      <c r="J7">
+      <c r="K7" s="1">
         <v>110.53</v>
       </c>
-      <c r="K7" t="s">
+      <c r="L7" t="s">
+        <v>38</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8">
+        <v>10</v>
+      </c>
+      <c r="D8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F8">
+        <v>39.35</v>
+      </c>
+      <c r="G8" t="s">
+        <v>32</v>
+      </c>
+      <c r="H8">
+        <v>1.49</v>
+      </c>
+      <c r="I8" s="1">
+        <v>58.63</v>
+      </c>
+      <c r="J8">
+        <v>1.55</v>
+      </c>
+      <c r="K8" s="1">
+        <v>60.99</v>
+      </c>
+      <c r="L8" t="s">
+        <v>39</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" t="s">
         <v>26</v>
       </c>
-      <c r="L7">
+      <c r="C9">
+        <v>10</v>
+      </c>
+      <c r="D9" t="s">
+        <v>30</v>
+      </c>
+      <c r="E9" t="s">
+        <v>31</v>
+      </c>
+      <c r="F9">
+        <v>35.06</v>
+      </c>
+      <c r="G9" t="s">
+        <v>32</v>
+      </c>
+      <c r="H9">
+        <v>1.5</v>
+      </c>
+      <c r="I9" s="1">
+        <v>52.59</v>
+      </c>
+      <c r="J9">
+        <v>1.57</v>
+      </c>
+      <c r="K9" s="1">
+        <v>55.04</v>
+      </c>
+      <c r="L9" t="s">
+        <v>40</v>
+      </c>
+      <c r="M9">
         <v>0</v>
       </c>
-      <c r="M7">
-        <v>178586</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-    </row>
-    <row r="11" spans="1:13">
-      <c r="A11" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B11" s="4" t="s">
+      <c r="N9" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10">
+        <v>11</v>
+      </c>
+      <c r="D10" t="s">
         <v>29</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="E10" t="s">
+        <v>31</v>
+      </c>
+      <c r="F10">
+        <v>72.84</v>
+      </c>
+      <c r="G10" t="s">
+        <v>32</v>
+      </c>
+      <c r="H10">
+        <v>1.5</v>
+      </c>
+      <c r="I10" s="1">
+        <v>109.26</v>
+      </c>
+      <c r="J10">
+        <v>1.57</v>
+      </c>
+      <c r="K10" s="1">
+        <v>114.36</v>
+      </c>
+      <c r="L10" t="s">
+        <v>41</v>
+      </c>
+      <c r="M10">
+        <v>104087</v>
+      </c>
+      <c r="N10" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11">
+        <v>10</v>
+      </c>
+      <c r="D11" t="s">
         <v>30</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="E11" t="s">
         <v>31</v>
       </c>
-      <c r="E11" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13">
-      <c r="A12" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B12" s="6">
-        <v>323.97</v>
-      </c>
-      <c r="C12" s="6">
-        <v>6</v>
-      </c>
-      <c r="D12" s="7">
-        <v>1.4661</v>
-      </c>
-      <c r="E12" s="6">
-        <v>474.96</v>
-      </c>
-      <c r="F12" s="6">
-        <v>497.41</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13">
-      <c r="A13" s="8" t="s">
+      <c r="F11">
+        <v>29.95</v>
+      </c>
+      <c r="G11" t="s">
         <v>32</v>
       </c>
-      <c r="B13" s="9">
-        <v>323.97</v>
-      </c>
-      <c r="C13" s="9">
-        <v>6</v>
-      </c>
-      <c r="D13" s="7"/>
-      <c r="E13" s="9">
-        <v>474.96</v>
-      </c>
-      <c r="F13" s="9">
-        <v>497.41</v>
+      <c r="H11">
+        <v>1.52</v>
+      </c>
+      <c r="I11" s="1">
+        <v>45.52</v>
+      </c>
+      <c r="J11">
+        <v>1.57</v>
+      </c>
+      <c r="K11" s="1">
+        <v>47.02</v>
+      </c>
+      <c r="L11" t="s">
+        <v>42</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12">
+        <v>11</v>
+      </c>
+      <c r="D12" t="s">
+        <v>29</v>
+      </c>
+      <c r="E12" t="s">
+        <v>31</v>
+      </c>
+      <c r="F12">
+        <v>68.77</v>
+      </c>
+      <c r="G12" t="s">
+        <v>32</v>
+      </c>
+      <c r="H12">
+        <v>1.52</v>
+      </c>
+      <c r="I12" s="1">
+        <v>104.53</v>
+      </c>
+      <c r="J12">
+        <v>1.57</v>
+      </c>
+      <c r="K12" s="1">
+        <v>107.97</v>
+      </c>
+      <c r="L12" t="s">
+        <v>43</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="6">
+        <v>569.9400000000001</v>
+      </c>
+      <c r="C17" s="6">
+        <v>11</v>
+      </c>
+      <c r="D17" s="7">
+        <v>1.4835</v>
+      </c>
+      <c r="E17" s="6">
+        <v>845.49</v>
+      </c>
+      <c r="F17" s="6">
+        <v>882.79</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="B18" s="9">
+        <v>569.9400000000001</v>
+      </c>
+      <c r="C18" s="9">
+        <v>11</v>
+      </c>
+      <c r="D18" s="7"/>
+      <c r="E18" s="9">
+        <v>845.49</v>
+      </c>
+      <c r="F18" s="9">
+        <v>882.79</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A15:F15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ПАНТЕКС АГРО ЕООД/ПАНТЕКС АГРО ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ПАНТЕКС АГРО ЕООД/ПАНТЕКС АГРО ЕООД.xlsx
@@ -232,7 +232,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -242,12 +242,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9EAF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDD7EE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -297,17 +291,17 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ПАНТЕКС АГРО ЕООД/ПАНТЕКС АГРО ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ПАНТЕКС АГРО ЕООД/ПАНТЕКС АГРО ЕООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="54">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -49,6 +52,12 @@
     <t>Час</t>
   </si>
   <si>
+    <t>Километри</t>
+  </si>
+  <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
     <t>2026-06-03</t>
   </si>
   <si>
@@ -67,13 +76,22 @@
     <t>2026-06-24</t>
   </si>
   <si>
-    <t>Варна Варненчик</t>
-  </si>
-  <si>
-    <t>Търговище</t>
-  </si>
-  <si>
-    <t>В.Търново</t>
+    <t>2026-06-27</t>
+  </si>
+  <si>
+    <t>2026-06-29</t>
+  </si>
+  <si>
+    <t>2026-06-30</t>
+  </si>
+  <si>
+    <t>1147 Варна Ситроен</t>
+  </si>
+  <si>
+    <t>1918 O5 Търговище</t>
+  </si>
+  <si>
+    <t>1103 Велико Търново изход</t>
   </si>
   <si>
     <t>78970154027720249</t>
@@ -85,22 +103,61 @@
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
-    <t>2026-06-03 08:31:14</t>
-  </si>
-  <si>
-    <t>2026-06-05 07:07:11</t>
-  </si>
-  <si>
-    <t>2026-06-09 09:22:51</t>
-  </si>
-  <si>
-    <t>2026-06-10 09:42:55</t>
-  </si>
-  <si>
-    <t>2026-06-22 07:21:04</t>
-  </si>
-  <si>
-    <t>2026-06-24 11:12:47</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>08:31:00</t>
+  </si>
+  <si>
+    <t>07:07:00</t>
+  </si>
+  <si>
+    <t>09:22:00</t>
+  </si>
+  <si>
+    <t>09:43:00</t>
+  </si>
+  <si>
+    <t>07:22:00</t>
+  </si>
+  <si>
+    <t>11:13:00</t>
+  </si>
+  <si>
+    <t>10:25:00</t>
+  </si>
+  <si>
+    <t>04:32:00</t>
+  </si>
+  <si>
+    <t>19:03:00</t>
+  </si>
+  <si>
+    <t>3232800816 3232800816</t>
+  </si>
+  <si>
+    <t>3232908146 3232908146</t>
+  </si>
+  <si>
+    <t>3233098323 3233098323</t>
+  </si>
+  <si>
+    <t>3233140662 3233140662</t>
+  </si>
+  <si>
+    <t>3233718126 3233718126</t>
+  </si>
+  <si>
+    <t>3233805635 3233805635</t>
+  </si>
+  <si>
+    <t>3233938355 3233938355</t>
+  </si>
+  <si>
+    <t>3234076366 3234076366</t>
+  </si>
+  <si>
+    <t>3234114373 3234114373</t>
   </si>
   <si>
     <t>Общи литри по продукт / ПАНТЕКС АГРО ЕООД</t>
@@ -518,7 +575,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -527,14 +584,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -568,288 +628,483 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C2">
         <v>11</v>
       </c>
       <c r="D2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="E2" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F2">
         <v>68.47</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H2">
         <v>1.52</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>104.07</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.57</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>107.5</v>
       </c>
-      <c r="K2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
+      <c r="L2" t="s">
+        <v>30</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C3">
         <v>10</v>
       </c>
       <c r="D3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E3" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F3">
         <v>34.41</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H3">
         <v>1.51</v>
       </c>
-      <c r="H3">
+      <c r="I3" s="1">
         <v>51.96</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3">
         <v>1.57</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="1">
         <v>54.02</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
+        <v>31</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
         <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" t="s">
-        <v>18</v>
       </c>
       <c r="C4">
         <v>10</v>
       </c>
       <c r="D4" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E4" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F4">
         <v>27.32</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H4">
         <v>1.48</v>
       </c>
-      <c r="H4">
+      <c r="I4" s="1">
         <v>40.43</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4">
         <v>1.56</v>
       </c>
-      <c r="J4">
+      <c r="K4" s="1">
         <v>42.62</v>
       </c>
-      <c r="K4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
+      <c r="L4" t="s">
+        <v>32</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C5">
         <v>11</v>
       </c>
       <c r="D5" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="E5" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F5">
         <v>67.93000000000001</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" t="s">
+        <v>29</v>
+      </c>
+      <c r="H5">
         <v>1.48</v>
       </c>
-      <c r="H5">
+      <c r="I5" s="1">
         <v>100.54</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J5">
         <v>1.56</v>
       </c>
-      <c r="J5">
+      <c r="K5" s="1">
         <v>105.97</v>
       </c>
-      <c r="K5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
+      <c r="L5" t="s">
+        <v>33</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C6">
         <v>10</v>
       </c>
       <c r="D6" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E6" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F6">
         <v>40.28</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" t="s">
+        <v>29</v>
+      </c>
+      <c r="H6">
         <v>1.43</v>
       </c>
-      <c r="H6">
+      <c r="I6" s="1">
         <v>57.6</v>
       </c>
-      <c r="I6" s="1">
+      <c r="J6">
         <v>1.5</v>
       </c>
-      <c r="J6">
+      <c r="K6" s="1">
         <v>60.42</v>
       </c>
-      <c r="K6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
+      <c r="L6" t="s">
+        <v>34</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C7">
         <v>11</v>
       </c>
       <c r="D7" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="E7" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F7">
         <v>53.46</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G7" t="s">
+        <v>29</v>
+      </c>
+      <c r="H7">
         <v>1.42</v>
       </c>
-      <c r="H7">
+      <c r="I7" s="1">
         <v>75.91</v>
       </c>
-      <c r="I7" s="1">
+      <c r="J7">
         <v>1.51</v>
       </c>
-      <c r="J7">
+      <c r="K7" s="1">
         <v>80.72</v>
       </c>
-      <c r="K7" t="s">
+      <c r="L7" t="s">
+        <v>35</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8">
+        <v>11</v>
+      </c>
+      <c r="D8" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="10" spans="1:11">
-      <c r="A10" s="3" t="s">
+      <c r="F8">
+        <v>60.06</v>
+      </c>
+      <c r="G8" t="s">
         <v>29</v>
       </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-    </row>
-    <row r="11" spans="1:11">
-      <c r="A11" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F11" s="4" t="s">
+      <c r="H8">
+        <v>1.41</v>
+      </c>
+      <c r="I8" s="1">
+        <v>84.68000000000001</v>
+      </c>
+      <c r="J8">
+        <v>1.5</v>
+      </c>
+      <c r="K8" s="1">
+        <v>90.09</v>
+      </c>
+      <c r="L8" t="s">
+        <v>36</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9">
+        <v>10</v>
+      </c>
+      <c r="D9" t="s">
+        <v>27</v>
+      </c>
+      <c r="E9" t="s">
+        <v>28</v>
+      </c>
+      <c r="F9">
+        <v>36.91</v>
+      </c>
+      <c r="G9" t="s">
+        <v>29</v>
+      </c>
+      <c r="H9">
+        <v>1.4</v>
+      </c>
+      <c r="I9" s="1">
+        <v>51.67</v>
+      </c>
+      <c r="J9">
+        <v>1.49</v>
+      </c>
+      <c r="K9" s="1">
+        <v>55</v>
+      </c>
+      <c r="L9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10">
+        <v>11</v>
+      </c>
+      <c r="D10" t="s">
+        <v>26</v>
+      </c>
+      <c r="E10" t="s">
+        <v>28</v>
+      </c>
+      <c r="F10">
+        <v>73.33</v>
+      </c>
+      <c r="G10" t="s">
+        <v>29</v>
+      </c>
+      <c r="H10">
+        <v>1.4</v>
+      </c>
+      <c r="I10" s="1">
+        <v>102.66</v>
+      </c>
+      <c r="J10">
+        <v>1.5</v>
+      </c>
+      <c r="K10" s="1">
+        <v>110</v>
+      </c>
+      <c r="L10" t="s">
+        <v>38</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" s="6">
+        <v>462.17</v>
+      </c>
+      <c r="C15" s="6">
         <v>9</v>
       </c>
-    </row>
-    <row r="12" spans="1:11">
-      <c r="A12" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B12" s="6">
-        <v>291.87</v>
-      </c>
-      <c r="C12" s="6">
-        <v>6</v>
-      </c>
-      <c r="D12" s="7">
-        <v>1.475</v>
-      </c>
-      <c r="E12" s="6">
-        <v>430.51</v>
-      </c>
-      <c r="F12" s="6">
-        <v>451.25</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
-      <c r="A13" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="B13" s="9">
-        <v>291.87</v>
-      </c>
-      <c r="C13" s="9">
-        <v>6</v>
-      </c>
-      <c r="D13" s="7"/>
-      <c r="E13" s="9">
-        <v>430.51</v>
-      </c>
-      <c r="F13" s="9">
-        <v>451.25</v>
+      <c r="D15" s="7">
+        <v>1.4486</v>
+      </c>
+      <c r="E15" s="6">
+        <v>669.52</v>
+      </c>
+      <c r="F15" s="6">
+        <v>706.34</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="B16" s="9">
+        <v>462.17</v>
+      </c>
+      <c r="C16" s="9">
+        <v>9</v>
+      </c>
+      <c r="D16" s="7"/>
+      <c r="E16" s="9">
+        <v>669.52</v>
+      </c>
+      <c r="F16" s="9">
+        <v>706.34</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A13:F13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ПАНТЕКС АГРО ЕООД/ПАНТЕКС АГРО ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ПАНТЕКС АГРО ЕООД/ПАНТЕКС АГРО ЕООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="69">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -52,6 +55,9 @@
     <t>Километри</t>
   </si>
   <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
     <t>2026-07-02</t>
   </si>
   <si>
@@ -64,28 +70,139 @@
     <t>2026-07-14</t>
   </si>
   <si>
-    <t>Търговище</t>
-  </si>
-  <si>
-    <t>В.Търново</t>
+    <t>2026-07-16</t>
+  </si>
+  <si>
+    <t>2026-07-17</t>
+  </si>
+  <si>
+    <t>2026-07-20</t>
+  </si>
+  <si>
+    <t>2026-07-23</t>
+  </si>
+  <si>
+    <t>2026-07-24</t>
+  </si>
+  <si>
+    <t>2026-07-26</t>
+  </si>
+  <si>
+    <t>2026-07-27</t>
+  </si>
+  <si>
+    <t>2026-07-29</t>
+  </si>
+  <si>
+    <t>2026-07-30</t>
+  </si>
+  <si>
+    <t>1918 O5 Търговище</t>
+  </si>
+  <si>
+    <t>1103 Велико Търново изход</t>
+  </si>
+  <si>
+    <t>1911 O5 Варна</t>
+  </si>
+  <si>
+    <t>1147 Варна Ситроен</t>
+  </si>
+  <si>
+    <t>1912 O5, Шумен 1</t>
   </si>
   <si>
     <t>78970154027720231</t>
   </si>
   <si>
+    <t>78970154027720249</t>
+  </si>
+  <si>
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
-    <t>2026-07-02 06:28:38</t>
-  </si>
-  <si>
-    <t>2026-07-07 20:06:44</t>
-  </si>
-  <si>
-    <t>2026-07-13 12:52:33</t>
-  </si>
-  <si>
-    <t>2026-07-14 07:50:28</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>06:28:00</t>
+  </si>
+  <si>
+    <t>20:08:00</t>
+  </si>
+  <si>
+    <t>12:53:00</t>
+  </si>
+  <si>
+    <t>07:50:00</t>
+  </si>
+  <si>
+    <t>09:32:00</t>
+  </si>
+  <si>
+    <t>12:22:00</t>
+  </si>
+  <si>
+    <t>07:24:00</t>
+  </si>
+  <si>
+    <t>17:18:00</t>
+  </si>
+  <si>
+    <t>11:52:00</t>
+  </si>
+  <si>
+    <t>18:00:00</t>
+  </si>
+  <si>
+    <t>18:55:00</t>
+  </si>
+  <si>
+    <t>06:26:00</t>
+  </si>
+  <si>
+    <t>19:14:00</t>
+  </si>
+  <si>
+    <t>3234200505 3234200505</t>
+  </si>
+  <si>
+    <t>3234434348 3234434348</t>
+  </si>
+  <si>
+    <t>3234744118 3234744118</t>
+  </si>
+  <si>
+    <t>3234786412 3234786412</t>
+  </si>
+  <si>
+    <t>3234875767 3234875767</t>
+  </si>
+  <si>
+    <t>3234937588 3234937588</t>
+  </si>
+  <si>
+    <t>3235092323 3235092323</t>
+  </si>
+  <si>
+    <t>3235241877 3235241877</t>
+  </si>
+  <si>
+    <t>3235305284 3235305284</t>
+  </si>
+  <si>
+    <t>3235364242 3235364242</t>
+  </si>
+  <si>
+    <t>3235451710 3235451710</t>
+  </si>
+  <si>
+    <t>3235531389 3235531389</t>
+  </si>
+  <si>
+    <t>3235525090 3235525090</t>
+  </si>
+  <si>
+    <t>3235596730 3235596730</t>
   </si>
   <si>
     <t>Общи литри по продукт / ПАНТЕКС АГРО ЕООД</t>
@@ -503,7 +620,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:N21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -512,15 +629,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -557,230 +676,700 @@
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="C2">
         <v>10</v>
       </c>
       <c r="D2" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="E2" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="F2">
         <v>30.43</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>35</v>
+      </c>
+      <c r="H2">
         <v>1.4</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>42.6</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.51</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>45.95</v>
       </c>
-      <c r="K2" t="s">
-        <v>20</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
+      <c r="L2" t="s">
+        <v>36</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="C3">
         <v>10</v>
       </c>
       <c r="D3" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="E3" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="F3">
         <v>44.15</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H3">
         <v>1.4</v>
       </c>
-      <c r="H3">
+      <c r="I3" s="1">
         <v>61.81</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3">
         <v>1.49</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="1">
         <v>65.78</v>
       </c>
-      <c r="K3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
+      <c r="L3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="C4">
         <v>10</v>
       </c>
       <c r="D4" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="E4" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="F4">
         <v>32.47</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" t="s">
+        <v>35</v>
+      </c>
+      <c r="H4">
         <v>1.4</v>
       </c>
-      <c r="H4">
+      <c r="I4" s="1">
         <v>45.46</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4">
         <v>1.5</v>
       </c>
-      <c r="J4">
+      <c r="K4" s="1">
         <v>48.7</v>
       </c>
-      <c r="K4" t="s">
-        <v>22</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
+      <c r="L4" t="s">
+        <v>38</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="C5">
         <v>10</v>
       </c>
       <c r="D5" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="E5" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="F5">
         <v>21.07</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H5">
         <v>1.41</v>
       </c>
-      <c r="H5">
+      <c r="I5" s="1">
         <v>29.71</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J5">
         <v>1.5</v>
       </c>
-      <c r="J5">
+      <c r="K5" s="1">
         <v>31.6</v>
       </c>
-      <c r="K5" t="s">
+      <c r="L5" t="s">
+        <v>39</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6">
+        <v>11</v>
+      </c>
+      <c r="D6" t="s">
+        <v>33</v>
+      </c>
+      <c r="E6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F6">
+        <v>48.74</v>
+      </c>
+      <c r="G6" t="s">
+        <v>35</v>
+      </c>
+      <c r="H6">
+        <v>1.41</v>
+      </c>
+      <c r="I6" s="1">
+        <v>68.72</v>
+      </c>
+      <c r="J6">
+        <v>1.5</v>
+      </c>
+      <c r="K6" s="1">
+        <v>73.11</v>
+      </c>
+      <c r="L6" t="s">
+        <v>40</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7">
+        <v>11</v>
+      </c>
+      <c r="D7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F7">
+        <v>58.57</v>
+      </c>
+      <c r="G7" t="s">
+        <v>35</v>
+      </c>
+      <c r="H7">
+        <v>1.41</v>
+      </c>
+      <c r="I7" s="1">
+        <v>82.58</v>
+      </c>
+      <c r="J7">
+        <v>1.51</v>
+      </c>
+      <c r="K7" s="1">
+        <v>88.44</v>
+      </c>
+      <c r="L7" t="s">
+        <v>41</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8">
+        <v>10</v>
+      </c>
+      <c r="D8" t="s">
+        <v>32</v>
+      </c>
+      <c r="E8" t="s">
+        <v>34</v>
+      </c>
+      <c r="F8">
+        <v>34.31</v>
+      </c>
+      <c r="G8" t="s">
+        <v>35</v>
+      </c>
+      <c r="H8">
+        <v>1.43</v>
+      </c>
+      <c r="I8" s="1">
+        <v>49.06</v>
+      </c>
+      <c r="J8">
+        <v>1.53</v>
+      </c>
+      <c r="K8" s="1">
+        <v>52.49</v>
+      </c>
+      <c r="L8" t="s">
+        <v>42</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9">
+        <v>11</v>
+      </c>
+      <c r="D9" t="s">
+        <v>33</v>
+      </c>
+      <c r="E9" t="s">
+        <v>34</v>
+      </c>
+      <c r="F9">
+        <v>58.07</v>
+      </c>
+      <c r="G9" t="s">
+        <v>35</v>
+      </c>
+      <c r="H9">
+        <v>1.44</v>
+      </c>
+      <c r="I9" s="1">
+        <v>83.62</v>
+      </c>
+      <c r="J9">
+        <v>1.54</v>
+      </c>
+      <c r="K9" s="1">
+        <v>89.43000000000001</v>
+      </c>
+      <c r="L9" t="s">
+        <v>43</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10">
+        <v>10</v>
+      </c>
+      <c r="D10" t="s">
+        <v>32</v>
+      </c>
+      <c r="E10" t="s">
+        <v>34</v>
+      </c>
+      <c r="F10">
+        <v>35.19</v>
+      </c>
+      <c r="G10" t="s">
+        <v>35</v>
+      </c>
+      <c r="H10">
+        <v>1.44</v>
+      </c>
+      <c r="I10" s="1">
+        <v>50.67</v>
+      </c>
+      <c r="J10">
+        <v>1.54</v>
+      </c>
+      <c r="K10" s="1">
+        <v>54.19</v>
+      </c>
+      <c r="L10" t="s">
+        <v>37</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" t="s">
         <v>23</v>
       </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
-      <c r="A8" s="3" t="s">
+      <c r="B11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11">
+        <v>11</v>
+      </c>
+      <c r="D11" t="s">
+        <v>33</v>
+      </c>
+      <c r="E11" t="s">
+        <v>34</v>
+      </c>
+      <c r="F11">
+        <v>45.95</v>
+      </c>
+      <c r="G11" t="s">
+        <v>35</v>
+      </c>
+      <c r="H11">
+        <v>1.44</v>
+      </c>
+      <c r="I11" s="1">
+        <v>66.17</v>
+      </c>
+      <c r="J11">
+        <v>1.56</v>
+      </c>
+      <c r="K11" s="1">
+        <v>71.68000000000001</v>
+      </c>
+      <c r="L11" t="s">
+        <v>44</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-    </row>
-    <row r="9" spans="1:12">
-      <c r="A9" s="4" t="s">
+      <c r="B12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12">
+        <v>11</v>
+      </c>
+      <c r="D12" t="s">
+        <v>33</v>
+      </c>
+      <c r="E12" t="s">
+        <v>34</v>
+      </c>
+      <c r="F12">
+        <v>65.38</v>
+      </c>
+      <c r="G12" t="s">
+        <v>35</v>
+      </c>
+      <c r="H12">
+        <v>1.44</v>
+      </c>
+      <c r="I12" s="1">
+        <v>94.15000000000001</v>
+      </c>
+      <c r="J12">
+        <v>1.56</v>
+      </c>
+      <c r="K12" s="1">
+        <v>101.99</v>
+      </c>
+      <c r="L12" t="s">
+        <v>45</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13">
+        <v>11</v>
+      </c>
+      <c r="D13" t="s">
+        <v>33</v>
+      </c>
+      <c r="E13" t="s">
+        <v>34</v>
+      </c>
+      <c r="F13">
+        <v>50.51</v>
+      </c>
+      <c r="G13" t="s">
+        <v>35</v>
+      </c>
+      <c r="H13">
+        <v>1.49</v>
+      </c>
+      <c r="I13" s="1">
+        <v>75.26000000000001</v>
+      </c>
+      <c r="J13">
+        <v>1.55</v>
+      </c>
+      <c r="K13" s="1">
+        <v>78.29000000000001</v>
+      </c>
+      <c r="L13" t="s">
+        <v>46</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14">
+        <v>10</v>
+      </c>
+      <c r="D14" t="s">
+        <v>32</v>
+      </c>
+      <c r="E14" t="s">
+        <v>34</v>
+      </c>
+      <c r="F14">
+        <v>39.19</v>
+      </c>
+      <c r="G14" t="s">
+        <v>35</v>
+      </c>
+      <c r="H14">
+        <v>1.49</v>
+      </c>
+      <c r="I14" s="1">
+        <v>58.39</v>
+      </c>
+      <c r="J14">
+        <v>1.55</v>
+      </c>
+      <c r="K14" s="1">
+        <v>60.74</v>
+      </c>
+      <c r="L14" t="s">
+        <v>47</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="B15" t="s">
         <v>27</v>
       </c>
-      <c r="D9" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12">
-      <c r="A10" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" s="6">
-        <v>128.12</v>
-      </c>
-      <c r="C10" s="6">
-        <v>4</v>
-      </c>
-      <c r="D10" s="7">
-        <v>1.4017</v>
-      </c>
-      <c r="E10" s="6">
-        <v>179.58</v>
-      </c>
-      <c r="F10" s="6">
-        <v>192.03</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12">
-      <c r="A11" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="B11" s="9">
-        <v>128.12</v>
-      </c>
-      <c r="C11" s="9">
-        <v>4</v>
-      </c>
-      <c r="D11" s="7"/>
-      <c r="E11" s="9">
-        <v>179.58</v>
-      </c>
-      <c r="F11" s="9">
-        <v>192.03</v>
+      <c r="C15">
+        <v>10</v>
+      </c>
+      <c r="D15" t="s">
+        <v>32</v>
+      </c>
+      <c r="E15" t="s">
+        <v>34</v>
+      </c>
+      <c r="F15">
+        <v>42.66</v>
+      </c>
+      <c r="G15" t="s">
+        <v>35</v>
+      </c>
+      <c r="H15">
+        <v>1.49</v>
+      </c>
+      <c r="I15" s="1">
+        <v>63.56</v>
+      </c>
+      <c r="J15">
+        <v>1.55</v>
+      </c>
+      <c r="K15" s="1">
+        <v>66.12</v>
+      </c>
+      <c r="L15" t="s">
+        <v>48</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B20" s="6">
+        <v>606.6900000000001</v>
+      </c>
+      <c r="C20" s="6">
+        <v>14</v>
+      </c>
+      <c r="D20" s="7">
+        <v>1.4369</v>
+      </c>
+      <c r="E20" s="6">
+        <v>871.76</v>
+      </c>
+      <c r="F20" s="6">
+        <v>928.51</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="B21" s="9">
+        <v>606.6900000000001</v>
+      </c>
+      <c r="C21" s="9">
+        <v>14</v>
+      </c>
+      <c r="D21" s="7"/>
+      <c r="E21" s="9">
+        <v>871.76</v>
+      </c>
+      <c r="F21" s="9">
+        <v>928.51</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A18:F18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ПАНТЕКС АГРО ЕООД/ПАНТЕКС АГРО ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ПАНТЕКС АГРО ЕООД/ПАНТЕКС АГРО ЕООД.xlsx
@@ -229,7 +229,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.000000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -1340,7 +1340,7 @@
         <v>14</v>
       </c>
       <c r="D20" s="7">
-        <v>1.4369</v>
+        <v>1.436912</v>
       </c>
       <c r="E20" s="6">
         <v>871.76</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ПАНТЕКС АГРО ЕООД/ПАНТЕКС АГРО ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ПАНТЕКС АГРО ЕООД/ПАНТЕКС АГРО ЕООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="70">
   <si>
     <t>Дата</t>
   </si>
@@ -35,6 +35,9 @@
   </si>
   <si>
     <t>Тип количество</t>
+  </si>
+  <si>
+    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -620,7 +623,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N21"/>
+  <dimension ref="A1:O21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -633,13 +636,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="10.7109375" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" customWidth="1"/>
+    <col min="15" max="15" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -682,626 +685,671 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C2">
         <v>10</v>
       </c>
       <c r="D2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F2">
         <v>30.43</v>
       </c>
       <c r="G2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H2">
-        <v>1.4</v>
+        <v>1.359</v>
       </c>
       <c r="I2" s="1">
-        <v>42.6</v>
+        <v>1.399</v>
       </c>
       <c r="J2">
+        <v>42.57157</v>
+      </c>
+      <c r="K2" s="1">
         <v>1.51</v>
       </c>
-      <c r="K2" s="1">
-        <v>45.95</v>
-      </c>
-      <c r="L2" t="s">
-        <v>36</v>
-      </c>
-      <c r="M2">
+      <c r="L2" s="1">
+        <v>45.9493</v>
+      </c>
+      <c r="M2" t="s">
+        <v>37</v>
+      </c>
+      <c r="N2">
         <v>0</v>
       </c>
-      <c r="N2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+      <c r="O2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C3">
         <v>10</v>
       </c>
       <c r="D3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F3">
-        <v>44.15</v>
+        <v>44.148</v>
       </c>
       <c r="G3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H3">
-        <v>1.4</v>
+        <v>1.359</v>
       </c>
       <c r="I3" s="1">
-        <v>61.81</v>
+        <v>1.399</v>
       </c>
       <c r="J3">
+        <v>61.763052</v>
+      </c>
+      <c r="K3" s="1">
         <v>1.49</v>
       </c>
-      <c r="K3" s="1">
-        <v>65.78</v>
-      </c>
-      <c r="L3" t="s">
-        <v>37</v>
-      </c>
-      <c r="M3">
+      <c r="L3" s="1">
+        <v>65.78052</v>
+      </c>
+      <c r="M3" t="s">
+        <v>38</v>
+      </c>
+      <c r="N3">
         <v>0</v>
       </c>
-      <c r="N3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+      <c r="O3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C4">
         <v>10</v>
       </c>
       <c r="D4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F4">
-        <v>32.47</v>
+        <v>32.473</v>
       </c>
       <c r="G4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H4">
-        <v>1.4</v>
+        <v>1.359</v>
       </c>
       <c r="I4" s="1">
-        <v>45.46</v>
+        <v>1.399</v>
       </c>
       <c r="J4">
+        <v>45.429727</v>
+      </c>
+      <c r="K4" s="1">
         <v>1.5</v>
       </c>
-      <c r="K4" s="1">
-        <v>48.7</v>
-      </c>
-      <c r="L4" t="s">
-        <v>38</v>
-      </c>
-      <c r="M4">
+      <c r="L4" s="1">
+        <v>48.7095</v>
+      </c>
+      <c r="M4" t="s">
+        <v>39</v>
+      </c>
+      <c r="N4">
         <v>0</v>
       </c>
-      <c r="N4" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+      <c r="O4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C5">
         <v>10</v>
       </c>
       <c r="D5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F5">
-        <v>21.07</v>
+        <v>21.073</v>
       </c>
       <c r="G5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H5">
-        <v>1.41</v>
+        <v>1.369</v>
       </c>
       <c r="I5" s="1">
-        <v>29.71</v>
+        <v>1.409</v>
       </c>
       <c r="J5">
+        <v>29.691857</v>
+      </c>
+      <c r="K5" s="1">
         <v>1.5</v>
       </c>
-      <c r="K5" s="1">
-        <v>31.6</v>
-      </c>
-      <c r="L5" t="s">
-        <v>39</v>
-      </c>
-      <c r="M5">
+      <c r="L5" s="1">
+        <v>31.6095</v>
+      </c>
+      <c r="M5" t="s">
+        <v>40</v>
+      </c>
+      <c r="N5">
         <v>0</v>
       </c>
-      <c r="N5" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
+      <c r="O5" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
       <c r="A6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C6">
         <v>11</v>
       </c>
       <c r="D6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F6">
         <v>48.74</v>
       </c>
       <c r="G6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H6">
-        <v>1.41</v>
+        <v>1.369</v>
       </c>
       <c r="I6" s="1">
-        <v>68.72</v>
+        <v>1.409</v>
       </c>
       <c r="J6">
+        <v>68.67466</v>
+      </c>
+      <c r="K6" s="1">
         <v>1.5</v>
       </c>
-      <c r="K6" s="1">
+      <c r="L6" s="1">
         <v>73.11</v>
       </c>
-      <c r="L6" t="s">
-        <v>40</v>
-      </c>
-      <c r="M6">
+      <c r="M6" t="s">
+        <v>41</v>
+      </c>
+      <c r="N6">
         <v>0</v>
       </c>
-      <c r="N6" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
+      <c r="O6" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
       <c r="A7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C7">
         <v>11</v>
       </c>
       <c r="D7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F7">
         <v>58.57</v>
       </c>
       <c r="G7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H7">
-        <v>1.41</v>
+        <v>1.369</v>
       </c>
       <c r="I7" s="1">
-        <v>82.58</v>
+        <v>1.409</v>
       </c>
       <c r="J7">
+        <v>82.52513</v>
+      </c>
+      <c r="K7" s="1">
         <v>1.51</v>
       </c>
-      <c r="K7" s="1">
-        <v>88.44</v>
-      </c>
-      <c r="L7" t="s">
-        <v>41</v>
-      </c>
-      <c r="M7">
+      <c r="L7" s="1">
+        <v>88.44070000000001</v>
+      </c>
+      <c r="M7" t="s">
+        <v>42</v>
+      </c>
+      <c r="N7">
         <v>0</v>
       </c>
-      <c r="N7" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
+      <c r="O7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C8">
         <v>10</v>
       </c>
       <c r="D8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F8">
-        <v>34.31</v>
+        <v>34.307</v>
       </c>
       <c r="G8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H8">
-        <v>1.43</v>
+        <v>1.389</v>
       </c>
       <c r="I8" s="1">
-        <v>49.06</v>
+        <v>1.429</v>
       </c>
       <c r="J8">
+        <v>49.024703</v>
+      </c>
+      <c r="K8" s="1">
         <v>1.53</v>
       </c>
-      <c r="K8" s="1">
-        <v>52.49</v>
-      </c>
-      <c r="L8" t="s">
-        <v>42</v>
-      </c>
-      <c r="M8">
+      <c r="L8" s="1">
+        <v>52.48971</v>
+      </c>
+      <c r="M8" t="s">
+        <v>43</v>
+      </c>
+      <c r="N8">
         <v>0</v>
       </c>
-      <c r="N8" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
+      <c r="O8" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C9">
         <v>11</v>
       </c>
       <c r="D9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F9">
-        <v>58.07</v>
+        <v>58.071</v>
       </c>
       <c r="G9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H9">
-        <v>1.44</v>
+        <v>1.401</v>
       </c>
       <c r="I9" s="1">
-        <v>83.62</v>
+        <v>1.441</v>
       </c>
       <c r="J9">
+        <v>83.680311</v>
+      </c>
+      <c r="K9" s="1">
         <v>1.54</v>
       </c>
-      <c r="K9" s="1">
-        <v>89.43000000000001</v>
-      </c>
-      <c r="L9" t="s">
-        <v>43</v>
-      </c>
-      <c r="M9">
+      <c r="L9" s="1">
+        <v>89.42934</v>
+      </c>
+      <c r="M9" t="s">
+        <v>44</v>
+      </c>
+      <c r="N9">
         <v>0</v>
       </c>
-      <c r="N9" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
+      <c r="O9" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C10">
         <v>10</v>
       </c>
       <c r="D10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F10">
-        <v>35.19</v>
+        <v>35.188</v>
       </c>
       <c r="G10" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H10">
-        <v>1.44</v>
+        <v>1.401</v>
       </c>
       <c r="I10" s="1">
-        <v>50.67</v>
+        <v>1.441</v>
       </c>
       <c r="J10">
+        <v>50.705908</v>
+      </c>
+      <c r="K10" s="1">
         <v>1.54</v>
       </c>
-      <c r="K10" s="1">
-        <v>54.19</v>
-      </c>
-      <c r="L10" t="s">
-        <v>37</v>
-      </c>
-      <c r="M10">
+      <c r="L10" s="1">
+        <v>54.18952</v>
+      </c>
+      <c r="M10" t="s">
+        <v>38</v>
+      </c>
+      <c r="N10">
         <v>0</v>
       </c>
-      <c r="N10" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
+      <c r="O10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C11">
         <v>11</v>
       </c>
       <c r="D11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F11">
-        <v>45.95</v>
+        <v>45.949</v>
       </c>
       <c r="G11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H11">
-        <v>1.44</v>
+        <v>1.401</v>
       </c>
       <c r="I11" s="1">
-        <v>66.17</v>
+        <v>1.441</v>
       </c>
       <c r="J11">
+        <v>66.212509</v>
+      </c>
+      <c r="K11" s="1">
         <v>1.56</v>
       </c>
-      <c r="K11" s="1">
-        <v>71.68000000000001</v>
-      </c>
-      <c r="L11" t="s">
-        <v>44</v>
-      </c>
-      <c r="M11">
+      <c r="L11" s="1">
+        <v>71.68044</v>
+      </c>
+      <c r="M11" t="s">
+        <v>45</v>
+      </c>
+      <c r="N11">
         <v>0</v>
       </c>
-      <c r="N11" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
+      <c r="O11" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
       <c r="A12" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C12">
         <v>11</v>
       </c>
       <c r="D12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E12" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F12">
-        <v>65.38</v>
+        <v>65.378</v>
       </c>
       <c r="G12" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H12">
-        <v>1.44</v>
+        <v>1.401</v>
       </c>
       <c r="I12" s="1">
-        <v>94.15000000000001</v>
+        <v>1.441</v>
       </c>
       <c r="J12">
+        <v>94.209698</v>
+      </c>
+      <c r="K12" s="1">
         <v>1.56</v>
       </c>
-      <c r="K12" s="1">
-        <v>101.99</v>
-      </c>
-      <c r="L12" t="s">
-        <v>45</v>
-      </c>
-      <c r="M12">
+      <c r="L12" s="1">
+        <v>101.98968</v>
+      </c>
+      <c r="M12" t="s">
+        <v>46</v>
+      </c>
+      <c r="N12">
         <v>0</v>
       </c>
-      <c r="N12" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
+      <c r="O12" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
       <c r="A13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C13">
         <v>11</v>
       </c>
       <c r="D13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F13">
         <v>50.51</v>
       </c>
       <c r="G13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H13">
-        <v>1.49</v>
+        <v>1.449</v>
       </c>
       <c r="I13" s="1">
-        <v>75.26000000000001</v>
+        <v>1.489</v>
       </c>
       <c r="J13">
+        <v>75.20939</v>
+      </c>
+      <c r="K13" s="1">
         <v>1.55</v>
       </c>
-      <c r="K13" s="1">
-        <v>78.29000000000001</v>
-      </c>
-      <c r="L13" t="s">
-        <v>46</v>
-      </c>
-      <c r="M13">
+      <c r="L13" s="1">
+        <v>78.29049999999999</v>
+      </c>
+      <c r="M13" t="s">
+        <v>47</v>
+      </c>
+      <c r="N13">
         <v>0</v>
       </c>
-      <c r="N13" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
+      <c r="O13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
       <c r="A14" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B14" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C14">
         <v>10</v>
       </c>
       <c r="D14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E14" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F14">
-        <v>39.19</v>
+        <v>39.187</v>
       </c>
       <c r="G14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H14">
-        <v>1.49</v>
+        <v>1.449</v>
       </c>
       <c r="I14" s="1">
-        <v>58.39</v>
+        <v>1.489</v>
       </c>
       <c r="J14">
+        <v>58.349443</v>
+      </c>
+      <c r="K14" s="1">
         <v>1.55</v>
       </c>
-      <c r="K14" s="1">
-        <v>60.74</v>
-      </c>
-      <c r="L14" t="s">
-        <v>47</v>
-      </c>
-      <c r="M14">
+      <c r="L14" s="1">
+        <v>60.73985</v>
+      </c>
+      <c r="M14" t="s">
+        <v>48</v>
+      </c>
+      <c r="N14">
         <v>0</v>
       </c>
-      <c r="N14" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
+      <c r="O14" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
       <c r="A15" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B15" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C15">
         <v>10</v>
       </c>
       <c r="D15" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E15" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F15">
-        <v>42.66</v>
+        <v>42.658</v>
       </c>
       <c r="G15" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H15">
-        <v>1.49</v>
+        <v>1.449</v>
       </c>
       <c r="I15" s="1">
-        <v>63.56</v>
+        <v>1.489</v>
       </c>
       <c r="J15">
+        <v>63.517762</v>
+      </c>
+      <c r="K15" s="1">
         <v>1.55</v>
       </c>
-      <c r="K15" s="1">
-        <v>66.12</v>
-      </c>
-      <c r="L15" t="s">
-        <v>48</v>
-      </c>
-      <c r="M15">
+      <c r="L15" s="1">
+        <v>66.1199</v>
+      </c>
+      <c r="M15" t="s">
+        <v>49</v>
+      </c>
+      <c r="N15">
         <v>0</v>
       </c>
-      <c r="N15" t="s">
-        <v>62</v>
+      <c r="O15" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
@@ -1311,60 +1359,60 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B20" s="6">
-        <v>606.6900000000001</v>
+        <v>606.682</v>
       </c>
       <c r="C20" s="6">
         <v>14</v>
       </c>
       <c r="D20" s="7">
-        <v>1.436912</v>
+        <v>1.43661</v>
       </c>
       <c r="E20" s="6">
-        <v>871.76</v>
+        <v>871.5700000000001</v>
       </c>
       <c r="F20" s="6">
-        <v>928.51</v>
+        <v>928.53</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B21" s="9">
-        <v>606.6900000000001</v>
+        <v>606.682</v>
       </c>
       <c r="C21" s="9">
         <v>14</v>
       </c>
       <c r="D21" s="7"/>
       <c r="E21" s="9">
-        <v>871.76</v>
+        <v>871.5700000000001</v>
       </c>
       <c r="F21" s="9">
-        <v>928.51</v>
+        <v>928.53</v>
       </c>
     </row>
   </sheetData>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ПАНТЕКС АГРО ЕООД/ПАНТЕКС АГРО ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ПАНТЕКС АГРО ЕООД/ПАНТЕКС АГРО ЕООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="69">
   <si>
     <t>Дата</t>
   </si>
@@ -35,9 +35,6 @@
   </si>
   <si>
     <t>Тип количество</t>
-  </si>
-  <si>
-    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -231,8 +228,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="#,##0.000000"/>
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -325,10 +322,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -623,7 +620,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O21"/>
+  <dimension ref="A1:N21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -636,13 +633,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="10.7109375" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" customWidth="1"/>
-    <col min="15" max="15" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -685,671 +682,626 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:15">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
       <c r="B2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C2">
         <v>10</v>
       </c>
       <c r="D2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F2">
         <v>30.43</v>
       </c>
       <c r="G2" t="s">
+        <v>35</v>
+      </c>
+      <c r="H2">
+        <v>1.399</v>
+      </c>
+      <c r="I2" s="1">
+        <v>42.572</v>
+      </c>
+      <c r="J2">
+        <v>1.51</v>
+      </c>
+      <c r="K2" s="1">
+        <v>45.949</v>
+      </c>
+      <c r="L2" t="s">
         <v>36</v>
       </c>
-      <c r="H2">
-        <v>1.359</v>
-      </c>
-      <c r="I2" s="1">
-        <v>1.399</v>
-      </c>
-      <c r="J2">
-        <v>42.57157</v>
-      </c>
-      <c r="K2" s="1">
-        <v>1.51</v>
-      </c>
-      <c r="L2" s="1">
-        <v>45.9493</v>
-      </c>
-      <c r="M2" t="s">
-        <v>37</v>
-      </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C3">
         <v>10</v>
       </c>
       <c r="D3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F3">
         <v>44.148</v>
       </c>
       <c r="G3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H3">
-        <v>1.359</v>
+        <v>1.399</v>
       </c>
       <c r="I3" s="1">
-        <v>1.399</v>
+        <v>61.763</v>
       </c>
       <c r="J3">
-        <v>61.763052</v>
+        <v>1.49</v>
       </c>
       <c r="K3" s="1">
-        <v>1.49</v>
-      </c>
-      <c r="L3" s="1">
-        <v>65.78052</v>
-      </c>
-      <c r="M3" t="s">
-        <v>38</v>
-      </c>
-      <c r="N3">
-        <v>0</v>
-      </c>
-      <c r="O3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+        <v>65.78100000000001</v>
+      </c>
+      <c r="L3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C4">
         <v>10</v>
       </c>
       <c r="D4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F4">
         <v>32.473</v>
       </c>
       <c r="G4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H4">
-        <v>1.359</v>
+        <v>1.399</v>
       </c>
       <c r="I4" s="1">
-        <v>1.399</v>
+        <v>45.43</v>
       </c>
       <c r="J4">
-        <v>45.429727</v>
+        <v>1.5</v>
       </c>
       <c r="K4" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="L4" s="1">
-        <v>48.7095</v>
-      </c>
-      <c r="M4" t="s">
-        <v>39</v>
-      </c>
-      <c r="N4">
-        <v>0</v>
-      </c>
-      <c r="O4" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
+        <v>48.71</v>
+      </c>
+      <c r="L4" t="s">
+        <v>38</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C5">
         <v>10</v>
       </c>
       <c r="D5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F5">
         <v>21.073</v>
       </c>
       <c r="G5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H5">
-        <v>1.369</v>
+        <v>1.409</v>
       </c>
       <c r="I5" s="1">
-        <v>1.409</v>
+        <v>29.692</v>
       </c>
       <c r="J5">
-        <v>29.691857</v>
+        <v>1.5</v>
       </c>
       <c r="K5" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="L5" s="1">
-        <v>31.6095</v>
-      </c>
-      <c r="M5" t="s">
-        <v>40</v>
-      </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
-      <c r="O5" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
+        <v>31.61</v>
+      </c>
+      <c r="L5" t="s">
+        <v>39</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C6">
         <v>11</v>
       </c>
       <c r="D6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F6">
         <v>48.74</v>
       </c>
       <c r="G6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H6">
-        <v>1.369</v>
+        <v>1.409</v>
       </c>
       <c r="I6" s="1">
-        <v>1.409</v>
+        <v>68.675</v>
       </c>
       <c r="J6">
-        <v>68.67466</v>
+        <v>1.5</v>
       </c>
       <c r="K6" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="L6" s="1">
         <v>73.11</v>
       </c>
-      <c r="M6" t="s">
-        <v>41</v>
-      </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
-      <c r="O6" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
+      <c r="L6" t="s">
+        <v>40</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C7">
         <v>11</v>
       </c>
       <c r="D7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F7">
         <v>58.57</v>
       </c>
       <c r="G7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H7">
-        <v>1.369</v>
+        <v>1.409</v>
       </c>
       <c r="I7" s="1">
-        <v>1.409</v>
+        <v>82.52500000000001</v>
       </c>
       <c r="J7">
-        <v>82.52513</v>
+        <v>1.51</v>
       </c>
       <c r="K7" s="1">
-        <v>1.51</v>
-      </c>
-      <c r="L7" s="1">
-        <v>88.44070000000001</v>
-      </c>
-      <c r="M7" t="s">
-        <v>42</v>
-      </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
-      <c r="O7" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
+        <v>88.441</v>
+      </c>
+      <c r="L7" t="s">
+        <v>41</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C8">
         <v>10</v>
       </c>
       <c r="D8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F8">
         <v>34.307</v>
       </c>
       <c r="G8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H8">
-        <v>1.389</v>
+        <v>1.429</v>
       </c>
       <c r="I8" s="1">
-        <v>1.429</v>
+        <v>49.025</v>
       </c>
       <c r="J8">
-        <v>49.024703</v>
+        <v>1.53</v>
       </c>
       <c r="K8" s="1">
-        <v>1.53</v>
-      </c>
-      <c r="L8" s="1">
-        <v>52.48971</v>
-      </c>
-      <c r="M8" t="s">
-        <v>43</v>
-      </c>
-      <c r="N8">
-        <v>0</v>
-      </c>
-      <c r="O8" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15">
+        <v>52.49</v>
+      </c>
+      <c r="L8" t="s">
+        <v>42</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C9">
         <v>11</v>
       </c>
       <c r="D9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F9">
         <v>58.071</v>
       </c>
       <c r="G9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H9">
-        <v>1.401</v>
+        <v>1.441</v>
       </c>
       <c r="I9" s="1">
-        <v>1.441</v>
+        <v>83.68000000000001</v>
       </c>
       <c r="J9">
-        <v>83.680311</v>
+        <v>1.54</v>
       </c>
       <c r="K9" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="L9" s="1">
-        <v>89.42934</v>
-      </c>
-      <c r="M9" t="s">
-        <v>44</v>
-      </c>
-      <c r="N9">
-        <v>0</v>
-      </c>
-      <c r="O9" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15">
+        <v>89.429</v>
+      </c>
+      <c r="L9" t="s">
+        <v>43</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C10">
         <v>10</v>
       </c>
       <c r="D10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E10" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F10">
         <v>35.188</v>
       </c>
       <c r="G10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H10">
-        <v>1.401</v>
+        <v>1.441</v>
       </c>
       <c r="I10" s="1">
-        <v>1.441</v>
+        <v>50.706</v>
       </c>
       <c r="J10">
-        <v>50.705908</v>
+        <v>1.54</v>
       </c>
       <c r="K10" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="L10" s="1">
-        <v>54.18952</v>
-      </c>
-      <c r="M10" t="s">
-        <v>38</v>
-      </c>
-      <c r="N10">
-        <v>0</v>
-      </c>
-      <c r="O10" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15">
+        <v>54.19</v>
+      </c>
+      <c r="L10" t="s">
+        <v>37</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C11">
         <v>11</v>
       </c>
       <c r="D11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F11">
         <v>45.949</v>
       </c>
       <c r="G11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H11">
-        <v>1.401</v>
+        <v>1.441</v>
       </c>
       <c r="I11" s="1">
-        <v>1.441</v>
+        <v>66.21299999999999</v>
       </c>
       <c r="J11">
-        <v>66.212509</v>
+        <v>1.56</v>
       </c>
       <c r="K11" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="L11" s="1">
-        <v>71.68044</v>
-      </c>
-      <c r="M11" t="s">
-        <v>45</v>
-      </c>
-      <c r="N11">
-        <v>0</v>
-      </c>
-      <c r="O11" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15">
+        <v>71.68000000000001</v>
+      </c>
+      <c r="L11" t="s">
+        <v>44</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C12">
         <v>11</v>
       </c>
       <c r="D12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F12">
         <v>65.378</v>
       </c>
       <c r="G12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H12">
-        <v>1.401</v>
+        <v>1.441</v>
       </c>
       <c r="I12" s="1">
-        <v>1.441</v>
+        <v>94.20999999999999</v>
       </c>
       <c r="J12">
-        <v>94.209698</v>
+        <v>1.56</v>
       </c>
       <c r="K12" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="L12" s="1">
-        <v>101.98968</v>
-      </c>
-      <c r="M12" t="s">
-        <v>46</v>
-      </c>
-      <c r="N12">
-        <v>0</v>
-      </c>
-      <c r="O12" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15">
+        <v>101.99</v>
+      </c>
+      <c r="L12" t="s">
+        <v>45</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C13">
         <v>11</v>
       </c>
       <c r="D13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F13">
         <v>50.51</v>
       </c>
       <c r="G13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H13">
-        <v>1.449</v>
+        <v>1.489</v>
       </c>
       <c r="I13" s="1">
-        <v>1.489</v>
+        <v>75.209</v>
       </c>
       <c r="J13">
-        <v>75.20939</v>
+        <v>1.55</v>
       </c>
       <c r="K13" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="L13" s="1">
-        <v>78.29049999999999</v>
-      </c>
-      <c r="M13" t="s">
-        <v>47</v>
-      </c>
-      <c r="N13">
-        <v>0</v>
-      </c>
-      <c r="O13" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15">
+        <v>78.29000000000001</v>
+      </c>
+      <c r="L13" t="s">
+        <v>46</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B14" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C14">
         <v>10</v>
       </c>
       <c r="D14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E14" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F14">
         <v>39.187</v>
       </c>
       <c r="G14" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H14">
-        <v>1.449</v>
+        <v>1.489</v>
       </c>
       <c r="I14" s="1">
-        <v>1.489</v>
+        <v>58.349</v>
       </c>
       <c r="J14">
-        <v>58.349443</v>
+        <v>1.55</v>
       </c>
       <c r="K14" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="L14" s="1">
-        <v>60.73985</v>
-      </c>
-      <c r="M14" t="s">
-        <v>48</v>
-      </c>
-      <c r="N14">
-        <v>0</v>
-      </c>
-      <c r="O14" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15">
+        <v>60.74</v>
+      </c>
+      <c r="L14" t="s">
+        <v>47</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
       <c r="A15" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15" t="s">
         <v>27</v>
-      </c>
-      <c r="B15" t="s">
-        <v>28</v>
       </c>
       <c r="C15">
         <v>10</v>
       </c>
       <c r="D15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F15">
         <v>42.658</v>
       </c>
       <c r="G15" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H15">
-        <v>1.449</v>
+        <v>1.489</v>
       </c>
       <c r="I15" s="1">
-        <v>1.489</v>
+        <v>63.518</v>
       </c>
       <c r="J15">
-        <v>63.517762</v>
+        <v>1.55</v>
       </c>
       <c r="K15" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="L15" s="1">
-        <v>66.1199</v>
-      </c>
-      <c r="M15" t="s">
-        <v>49</v>
-      </c>
-      <c r="N15">
-        <v>0</v>
-      </c>
-      <c r="O15" t="s">
-        <v>63</v>
+        <v>66.12</v>
+      </c>
+      <c r="L15" t="s">
+        <v>48</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
@@ -1359,47 +1311,47 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B19" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="C19" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="D19" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="D19" s="4" t="s">
-        <v>68</v>
-      </c>
       <c r="E19" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B20" s="6">
         <v>606.682</v>
       </c>
-      <c r="C20" s="6">
+      <c r="C20" s="7">
         <v>14</v>
       </c>
       <c r="D20" s="7">
-        <v>1.43661</v>
-      </c>
-      <c r="E20" s="6">
-        <v>871.5700000000001</v>
-      </c>
-      <c r="F20" s="6">
+        <v>1.437</v>
+      </c>
+      <c r="E20" s="7">
+        <v>871.567</v>
+      </c>
+      <c r="F20" s="7">
         <v>928.53</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B21" s="9">
         <v>606.682</v>
@@ -1409,7 +1361,7 @@
       </c>
       <c r="D21" s="7"/>
       <c r="E21" s="9">
-        <v>871.5700000000001</v>
+        <v>871.567</v>
       </c>
       <c r="F21" s="9">
         <v>928.53</v>
